--- a/backend/dynamic_live_backup.xlsx
+++ b/backend/dynamic_live_backup.xlsx
@@ -19392,19 +19392,19 @@
         <v>30367675</v>
       </c>
       <c r="F594" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G594" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
       <c r="H594" t="str">
-        <v>28/05/2026</v>
+        <v/>
       </c>
       <c r="I594" t="str">
-        <v>Thursday</v>
+        <v/>
       </c>
       <c r="J594" t="str">
-        <v>15:17:53</v>
+        <v/>
       </c>
     </row>
     <row r="595">

--- a/backend/dynamic_live_backup.xlsx
+++ b/backend/dynamic_live_backup.xlsx
@@ -8707,7 +8707,7 @@
         <v>Given</v>
       </c>
       <c r="G260" t="str">
-        <v>Ilyas</v>
+        <v>Ilyas Saroda</v>
       </c>
       <c r="H260" t="str">
         <v/>
